--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T14:23:39+00:00</t>
+    <t>2026-01-28T15:00:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -739,14 +739,14 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-encounter-identifier-cs"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-encounter-identifier"/&gt;
     &lt;code value="SEJ"/&gt;
     &lt;display value="Identifiant du séjour"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-encounter-identifier-vs|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-encounter-identifier|2.2.0-ballot</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -2193,7 +2193,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="64.00390625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="73.91015625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.59375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T15:00:38+00:00</t>
+    <t>2026-01-28T15:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T15:51:30+00:00</t>
+    <t>2026-02-02T09:49:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T09:49:54+00:00</t>
+    <t>2026-02-02T14:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T14:44:55+00:00</t>
+    <t>2026-02-04T16:15:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T16:15:13+00:00</t>
+    <t>2026-02-05T08:25:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
